--- a/dados/excel/gini_mensal.xlsx
+++ b/dados/excel/gini_mensal.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Série temporal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Série temporal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$D$58</definedName>
@@ -628,7 +628,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/gini_mensal.xlsx
+++ b/dados/excel/gini_mensal.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
